--- a/reports/m2141-ramadhan final_annotated_review_sheet.xlsx
+++ b/reports/m2141-ramadhan final_annotated_review_sheet.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -501,12 +501,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>[IEEE Copyright Notice] Missing IEEE Copyright Notice in the bottom-left of page 1. IEEE conference proceedings require the copyright clearance code line (e.g. 979-8-... ©20XX IEEE) in the footer.</t>
+          <t>[Figure Citation] Found "Figure 2". IEEE rule prescribes: 'Use the abbreviation "Fig. 1", even at the beginning of a sentence.' (Do not spell out 'Figure').</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Page 1, Bottom Left Footer</t>
+          <t>Page 3, Right Column, Lower-Middle Section</t>
         </is>
       </c>
     </row>
@@ -516,12 +516,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>[Figure Citation] Found "Figure 2". IEEE rule prescribes: 'Use the abbreviation "Fig. 1", even at the beginning of a sentence.' (Do not spell out 'Figure').</t>
+          <t>[Figure Citation] Found "Figure 6". IEEE rule prescribes: 'Use the abbreviation "Fig. 1", even at the beginning of a sentence.' (Do not spell out 'Figure').</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Page 3, Right Column, Lower-Middle Section</t>
+          <t>Page 5, Left Column, Top Section</t>
         </is>
       </c>
     </row>
@@ -531,12 +531,13 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>[Figure Citation] Found "Figure 6". IEEE rule prescribes: 'Use the abbreviation "Fig. 1", even at the beginning of a sentence.' (Do not spell out 'Figure').</t>
+          <t>[Citation Punctuation] Found sentence punctuation placed before citation bracket: "z. 
+[4]". IEEE rule: 'The sentence punctuation follows the bracket [2].' (e.g. use '...word [1].' instead of '...word.[1]').</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Page 5, Left Column, Top Section</t>
+          <t>Page 7, Left Column, Top Section</t>
         </is>
       </c>
     </row>
@@ -546,13 +547,13 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>[Citation Punctuation] Found sentence punctuation placed before citation bracket: "z. 
-[4]". IEEE rule: 'The sentence punctuation follows the bracket [2].' (e.g. use '...word [1].' instead of '...word.[1]').</t>
+          <t>[Citation Punctuation] Found sentence punctuation placed before citation bracket: "indonesia. 
+[14]". IEEE rule: 'The sentence punctuation follows the bracket [2].' (e.g. use '...word [1].' instead of '...word.[1]').</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Page 7, Left Column, Top Section</t>
+          <t>Page 7, Left Column, Lower-Middle Section</t>
         </is>
       </c>
     </row>
@@ -562,27 +563,11 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>[Citation Punctuation] Found sentence punctuation placed before citation bracket: "indonesia. 
-[14]". IEEE rule: 'The sentence punctuation follows the bracket [2].' (e.g. use '...word [1].' instead of '...word.[1]').</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Page 7, Left Column, Lower-Middle Section</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
           <t>[Citation Punctuation] Found sentence punctuation placed before citation bracket: "x. 
 [15]". IEEE rule: 'The sentence punctuation follows the bracket [2].' (e.g. use '...word [1].' instead of '...word.[1]').</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Page 7, Left Column, Lower-Middle Section</t>
         </is>
